--- a/exports/MAZDOCK_full_report.xlsx
+++ b/exports/MAZDOCK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.33</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>137.1</v>
+        <v>130.9</v>
       </c>
       <c r="I2" t="n">
         <v>133.1947070694282</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.7</v>
+        <v>-7.1</v>
       </c>
       <c r="L2" t="n">
-        <v>4.36</v>
+        <v>7.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>6.67</v>
       </c>
       <c r="O2" t="n">
         <v>0.18</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>120.6</v>
+        <v>123.3</v>
       </c>
       <c r="I3" t="n">
         <v>122.2913682776499</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K3" t="n">
-        <v>7.87</v>
+        <v>5.81</v>
       </c>
       <c r="L3" t="n">
         <v>6.34</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44648.38541666666</v>
+        <v>44648.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>122</v>
+        <v>120.8</v>
       </c>
       <c r="I4" t="n">
         <v>120.8061079693577</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.05</v>
+        <v>-2.03</v>
       </c>
       <c r="L4" t="n">
         <v>4.46</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>6.52</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>125.3</v>
+        <v>137</v>
       </c>
       <c r="I5" t="n">
         <v>126.5494489715031</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.73</v>
+        <v>-13.41</v>
       </c>
       <c r="L5" t="n">
-        <v>4.3</v>
+        <v>15.89</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.68</v>
+        <v>8.06</v>
       </c>
       <c r="O5" t="n">
         <v>-2.93</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.65</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44686.38541666666</v>
+        <v>44686.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>146.3</v>
+        <v>143.2</v>
       </c>
       <c r="I6" t="n">
         <v>144.9392179908047</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>6.79</v>
+        <v>4.53</v>
       </c>
       <c r="L6" t="n">
         <v>7.66</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.42</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44700.55208333334</v>
+        <v>44701.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>143.4</v>
+        <v>148.7</v>
       </c>
       <c r="I7" t="n">
         <v>147.2240012344536</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.14</v>
+        <v>-3.84</v>
       </c>
       <c r="L7" t="n">
-        <v>3.91</v>
+        <v>6.22</v>
       </c>
       <c r="M7" t="n">
         <v>1.58</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>11.38</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44720.55208333334</v>
+        <v>44721.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>135.5</v>
+        <v>133.5</v>
       </c>
       <c r="I8" t="n">
         <v>134.7150501817713</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.880000000000001</v>
+        <v>-10.22</v>
       </c>
       <c r="L8" t="n">
-        <v>9.41</v>
+        <v>10.39</v>
       </c>
       <c r="M8" t="n">
         <v>2.81</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.65</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44740.38541666666</v>
+        <v>44740.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>127.35</v>
+        <v>128.2</v>
       </c>
       <c r="I9" t="n">
         <v>128.0787802486014</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>4.61</v>
+        <v>3.97</v>
       </c>
       <c r="L9" t="n">
         <v>1.35</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.28</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>408.5</v>
+        <v>389.3</v>
       </c>
       <c r="I10" t="n">
         <v>393.6347757800121</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>143</v>
+        <v>145.8333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>218.64</v>
+        <v>203.67</v>
       </c>
       <c r="L10" t="n">
         <v>5.77</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>194</v>
+        <v>195</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>14.25</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44887.55208333334</v>
+        <v>44888.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>430.6</v>
+        <v>447.5</v>
       </c>
       <c r="I11" t="n">
         <v>432.3491411107341</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>-10.61</v>
+        <v>-14.95</v>
       </c>
       <c r="L11" t="n">
-        <v>12.77</v>
+        <v>17.26</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
         <v>11.68</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>13.29</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>422</v>
+        <v>417.15</v>
       </c>
       <c r="I12" t="n">
         <v>421.9360520301105</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.7</v>
+        <v>-6.78</v>
       </c>
       <c r="L12" t="n">
-        <v>6.63</v>
+        <v>7.78</v>
       </c>
       <c r="M12" t="n">
         <v>0.44</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>7.99</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44921.55208333334</v>
+        <v>44922.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>406</v>
+        <v>410.1</v>
       </c>
       <c r="I13" t="n">
         <v>409.6681901328472</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>2.67</v>
+        <v>1.69</v>
       </c>
       <c r="L13" t="n">
         <v>7.13</v>
       </c>
       <c r="M13" t="n">
-        <v>0.71</v>
+        <v>1.35</v>
       </c>
       <c r="N13" t="n">
         <v>15.67</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>14.13</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44944.55208333334</v>
+        <v>44945.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>379.9</v>
+        <v>372.15</v>
       </c>
       <c r="I14" t="n">
         <v>372.5389567592447</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.36</v>
+        <v>-9.25</v>
       </c>
       <c r="L14" t="n">
-        <v>7.63</v>
+        <v>9.51</v>
       </c>
       <c r="M14" t="n">
         <v>1.31</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
         <v>0.79</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.64</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>326</v>
+        <v>336.1</v>
       </c>
       <c r="I15" t="n">
         <v>336.0417332721186</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>71</v>
       </c>
       <c r="K15" t="n">
-        <v>12.4</v>
+        <v>9.69</v>
       </c>
       <c r="L15" t="n">
         <v>8.01</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.42</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>386.6</v>
+        <v>373.6</v>
       </c>
       <c r="I16" t="n">
         <v>379.9570413967525</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K16" t="n">
-        <v>15.03</v>
+        <v>11.16</v>
       </c>
       <c r="L16" t="n">
         <v>3.27</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="N16" t="n">
-        <v>2.04</v>
+        <v>3.97</v>
       </c>
       <c r="O16" t="n">
         <v>1.3</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>8.92</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45076.38541666666</v>
+        <v>45076.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>388.6</v>
+        <v>407</v>
       </c>
       <c r="I17" t="n">
         <v>399.5450882410855</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.01</v>
+        <v>-8.94</v>
       </c>
       <c r="L17" t="n">
-        <v>4.9</v>
+        <v>9.07</v>
       </c>
       <c r="M17" t="n">
         <v>0.6</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.99</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45148.38541666666</v>
+        <v>45148.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>914.6</v>
+        <v>898</v>
       </c>
       <c r="I18" t="n">
         <v>902.1714988847269</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>71.83333333333333</v>
+        <v>72</v>
       </c>
       <c r="K18" t="n">
-        <v>124.72</v>
+        <v>120.64</v>
       </c>
       <c r="L18" t="n">
         <v>5.04</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>8.34</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45152.55208333334</v>
+        <v>45154.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>935.5</v>
+        <v>973.9</v>
       </c>
       <c r="I19" t="n">
         <v>958.2888098228573</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.18</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>6.84</v>
+        <v>10.02</v>
       </c>
       <c r="M19" t="n">
         <v>0.25</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>12.4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1049</v>
+        <v>1016.8</v>
       </c>
       <c r="I20" t="n">
         <v>1031.282897741525</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K20" t="n">
-        <v>7.71</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
         <v>6.82</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="N20" t="n">
         <v>7.37</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>17.49</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45226.38541666666</v>
+        <v>45226.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>983.7</v>
+        <v>1025</v>
       </c>
       <c r="I21" t="n">
         <v>997.6171012181852</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>3.26</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>16.05</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>13.39</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45323.55208333334</v>
+        <v>45324.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1116.5</v>
+        <v>1102</v>
       </c>
       <c r="I22" t="n">
         <v>1115.534916852822</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>97</v>
+        <v>97.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>8.93</v>
+        <v>7.51</v>
       </c>
       <c r="L22" t="n">
         <v>7.6</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.17</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>930.75</v>
+        <v>1004.7</v>
       </c>
       <c r="I23" t="n">
         <v>999.7243934875372</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K23" t="n">
-        <v>15.54</v>
+        <v>8.83</v>
       </c>
       <c r="L23" t="n">
         <v>2.54</v>
@@ -1752,7 +2027,7 @@
         <v>2.58</v>
       </c>
       <c r="N23" t="n">
-        <v>4.15</v>
+        <v>7.44</v>
       </c>
       <c r="O23" t="n">
         <v>-1.21</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.15</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1133.5</v>
+        <v>1084</v>
       </c>
       <c r="I24" t="n">
         <v>1105.72699891199</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K24" t="n">
-        <v>12.82</v>
+        <v>7.89</v>
       </c>
       <c r="L24" t="n">
         <v>6.44</v>
@@ -1809,7 +2096,7 @@
         <v>2.63</v>
       </c>
       <c r="N24" t="n">
-        <v>3.86</v>
+        <v>4.28</v>
       </c>
       <c r="O24" t="n">
         <v>7.44</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>14.31</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45426.38541666666</v>
+        <v>45426.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1127.4</v>
+        <v>1174.5</v>
       </c>
       <c r="I25" t="n">
         <v>1170.759493553888</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-4</v>
+        <v>-8.35</v>
       </c>
       <c r="L25" t="n">
-        <v>6.93</v>
+        <v>8.99</v>
       </c>
       <c r="M25" t="n">
         <v>0.66</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>12.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1624.5</v>
+        <v>1410.5</v>
       </c>
       <c r="I26" t="n">
         <v>1460.434347994629</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>38.31</v>
+        <v>20.09</v>
       </c>
       <c r="L26" t="n">
         <v>4.02</v>
       </c>
       <c r="M26" t="n">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>15.98</v>
       </c>
       <c r="O26" t="n">
         <v>10.28</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>24.21</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45456.55208333334</v>
+        <v>45457.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1692.5</v>
+        <v>1780.5</v>
       </c>
       <c r="I27" t="n">
         <v>1696.796511859083</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>-19.99</v>
+        <v>-26.23</v>
       </c>
       <c r="L27" t="n">
-        <v>20.88</v>
+        <v>27.25</v>
       </c>
       <c r="M27" t="n">
         <v>1.18</v>
       </c>
       <c r="N27" t="n">
-        <v>13.16</v>
+        <v>14.12</v>
       </c>
       <c r="O27" t="n">
         <v>-15.98</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>15.26</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45497.55208333334</v>
+        <v>45498.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>2518.5</v>
+        <v>2450</v>
       </c>
       <c r="I28" t="n">
         <v>2459.345404590324</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K28" t="n">
-        <v>41.45</v>
+        <v>37.6</v>
       </c>
       <c r="L28" t="n">
         <v>5.78</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>14.65</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45502.55208333334</v>
+        <v>45503.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>2672</v>
+        <v>2711.7</v>
       </c>
       <c r="I29" t="n">
         <v>2707.745333108064</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>-9.06</v>
+        <v>-10.68</v>
       </c>
       <c r="L29" t="n">
-        <v>9.06</v>
+        <v>13.17</v>
       </c>
       <c r="M29" t="n">
         <v>0.77</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>11.74</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>2545</v>
+        <v>2394</v>
       </c>
       <c r="I30" t="n">
         <v>2406.770636947799</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.15</v>
+        <v>-11.72</v>
       </c>
       <c r="L30" t="n">
-        <v>7.99</v>
+        <v>12.75</v>
       </c>
       <c r="M30" t="n">
-        <v>2.25</v>
+        <v>4.89</v>
       </c>
       <c r="N30" t="n">
-        <v>2.48</v>
+        <v>6.03</v>
       </c>
       <c r="O30" t="n">
         <v>0.21</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.82</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>2227.5</v>
+        <v>2362.5</v>
       </c>
       <c r="I31" t="n">
         <v>2284.900719868472</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K31" t="n">
-        <v>6.95</v>
+        <v>1.32</v>
       </c>
       <c r="L31" t="n">
         <v>7.66</v>
@@ -2208,7 +2579,7 @@
         <v>3</v>
       </c>
       <c r="N31" t="n">
-        <v>6.15</v>
+        <v>7.45</v>
       </c>
       <c r="O31" t="n">
         <v>-6.03</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>12.42</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>2153.5</v>
+        <v>2129.7</v>
       </c>
       <c r="I32" t="n">
         <v>2148.949957694295</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>-8.85</v>
+        <v>-9.85</v>
       </c>
       <c r="L32" t="n">
-        <v>9.630000000000001</v>
+        <v>10.03</v>
       </c>
       <c r="M32" t="n">
         <v>0.05</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45554.55208333334</v>
+        <v>45555.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>2031</v>
+        <v>2191</v>
       </c>
       <c r="I33" t="n">
         <v>2184.733425998769</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>4.63</v>
+        <v>-2.88</v>
       </c>
       <c r="L33" t="n">
-        <v>1.86</v>
+        <v>3.65</v>
       </c>
       <c r="M33" t="n">
         <v>0.77</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="O33" t="n">
         <v>-1.25</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>13.05</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>2039.4</v>
+        <v>1961.4</v>
       </c>
       <c r="I34" t="n">
         <v>1991.552432446897</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.92</v>
+        <v>-10.48</v>
       </c>
       <c r="L34" t="n">
-        <v>9.289999999999999</v>
+        <v>11.15</v>
       </c>
       <c r="M34" t="n">
         <v>1.31</v>
       </c>
       <c r="N34" t="n">
-        <v>2.69</v>
+        <v>3.67</v>
       </c>
       <c r="O34" t="n">
         <v>7.41</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>9.69</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45574.55208333334</v>
+        <v>45575.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>2046</v>
+        <v>2214.9</v>
       </c>
       <c r="I35" t="n">
         <v>2103.451205827445</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.31</v>
+        <v>-12.92</v>
       </c>
       <c r="L35" t="n">
-        <v>6.32</v>
+        <v>14.97</v>
       </c>
       <c r="M35" t="n">
-        <v>0.42</v>
+        <v>1.54</v>
       </c>
       <c r="N35" t="n">
-        <v>4.17</v>
+        <v>8.26</v>
       </c>
       <c r="O35" t="n">
         <v>-3.67</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>11.18</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45587.38541666666</v>
+        <v>45587.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>2134.1</v>
+        <v>2104</v>
       </c>
       <c r="I36" t="n">
         <v>2111.449285038321</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.65</v>
+        <v>-5.01</v>
       </c>
       <c r="L36" t="n">
-        <v>6.32</v>
+        <v>7.08</v>
       </c>
       <c r="M36" t="n">
         <v>0.05</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>12.76</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>2086</v>
+        <v>2138.8</v>
       </c>
       <c r="I37" t="n">
         <v>2102.474241095182</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>0.86</v>
+        <v>-1.65</v>
       </c>
       <c r="L37" t="n">
-        <v>4.25</v>
+        <v>5.65</v>
       </c>
       <c r="M37" t="n">
         <v>4.51</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.18</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>2527.5</v>
+        <v>2406.9</v>
       </c>
       <c r="I38" t="n">
         <v>2461.371405537175</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>18.17</v>
+        <v>12.54</v>
       </c>
       <c r="L38" t="n">
         <v>2.83</v>
@@ -2607,7 +3062,7 @@
         <v>2.72</v>
       </c>
       <c r="N38" t="n">
-        <v>3.58</v>
+        <v>6.43</v>
       </c>
       <c r="O38" t="n">
         <v>1.98</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.79</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>2250</v>
+        <v>2314.25</v>
       </c>
       <c r="I39" t="n">
         <v>2282.295467018936</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K39" t="n">
-        <v>6.52</v>
+        <v>3.85</v>
       </c>
       <c r="L39" t="n">
         <v>6.86</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.03</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45691.55208333334</v>
+        <v>45692.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>2235</v>
+        <v>2200.85</v>
       </c>
       <c r="I40" t="n">
         <v>2228.99943442618</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.42</v>
+        <v>-4.9</v>
       </c>
       <c r="L40" t="n">
         <v>9.93</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>16.05</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>2168.15</v>
+        <v>2225.95</v>
       </c>
       <c r="I41" t="n">
         <v>2215.149531164999</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K41" t="n">
-        <v>1.49</v>
+        <v>-1.14</v>
       </c>
       <c r="L41" t="n">
         <v>10.86</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>11.15</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2537.9</v>
+        <v>2298.7</v>
       </c>
       <c r="I42" t="n">
         <v>2494.524643282025</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K42" t="n">
-        <v>14.01</v>
+        <v>3.27</v>
       </c>
       <c r="L42" t="n">
         <v>3.36</v>
       </c>
       <c r="M42" t="n">
-        <v>5.95</v>
+        <v>12.48</v>
       </c>
       <c r="N42" t="n">
-        <v>7.31</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="O42" t="n">
         <v>3.68</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>13.51</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2435.5</v>
+        <v>2665</v>
       </c>
       <c r="I43" t="n">
         <v>2609.365760047403</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.95</v>
+        <v>-15.94</v>
       </c>
       <c r="L43" t="n">
-        <v>7.58</v>
+        <v>16.15</v>
       </c>
       <c r="M43" t="n">
         <v>3.54</v>
       </c>
       <c r="N43" t="n">
-        <v>2.67</v>
+        <v>8.93</v>
       </c>
       <c r="O43" t="n">
         <v>-8.279999999999999</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>14.86</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>3475</v>
+        <v>3400</v>
       </c>
       <c r="I44" t="n">
         <v>3474.312887127024</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K44" t="n">
-        <v>30.39</v>
+        <v>27.58</v>
       </c>
       <c r="L44" t="n">
         <v>7.2</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.85</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45910.55208333334</v>
+        <v>45911.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>2759.9</v>
+        <v>2774.2</v>
       </c>
       <c r="I45" t="n">
         <v>2773.798443735579</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>100.1666666666667</v>
+        <v>101</v>
       </c>
       <c r="K45" t="n">
-        <v>18.83</v>
+        <v>18.41</v>
       </c>
       <c r="L45" t="n">
         <v>4.37</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.41</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2924.3</v>
+        <v>2868</v>
       </c>
       <c r="I46" t="n">
         <v>2887.953174877011</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>5.41</v>
+        <v>3.38</v>
       </c>
       <c r="L46" t="n">
         <v>0.73</v>
@@ -3063,7 +3614,7 @@
         <v>0.18</v>
       </c>
       <c r="N46" t="n">
-        <v>0.97</v>
+        <v>2.99</v>
       </c>
       <c r="O46" t="n">
         <v>1.45</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.02</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45971.55208333334</v>
+        <v>45972.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2707</v>
+        <v>2747.6</v>
       </c>
       <c r="I47" t="n">
         <v>2740.007289853266</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K47" t="n">
-        <v>5.61</v>
+        <v>4.2</v>
       </c>
       <c r="L47" t="n">
         <v>2.15</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>5.47</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45982.55208333334</v>
+        <v>45985.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>2741.1</v>
+        <v>2700.4</v>
       </c>
       <c r="I48" t="n">
         <v>2724.507064480019</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.24</v>
+        <v>-1.72</v>
       </c>
       <c r="L48" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="M48" t="n">
-        <v>0.33</v>
+        <v>0.59</v>
       </c>
       <c r="N48" t="n">
         <v>3.18</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>2406.8</v>
+        <v>2545</v>
       </c>
       <c r="I49" t="n">
         <v>2473.962052632903</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K49" t="n">
-        <v>10.87</v>
+        <v>5.75</v>
       </c>
       <c r="L49" t="n">
         <v>1.13</v>
@@ -3234,7 +3821,7 @@
         <v>0.71</v>
       </c>
       <c r="N49" t="n">
-        <v>2.33</v>
+        <v>5.74</v>
       </c>
       <c r="O49" t="n">
         <v>-1.94</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.69</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46041.38541666666</v>
+        <v>46041.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>2436.1</v>
+        <v>2432</v>
       </c>
       <c r="I50" t="n">
         <v>2433.965748587229</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.28</v>
+        <v>-4.44</v>
       </c>
       <c r="L50" t="n">
         <v>5.65</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>5.89</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>2350</v>
+        <v>2459.5</v>
       </c>
       <c r="I51" t="n">
         <v>2458.815860056552</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>3.37</v>
+        <v>-1.13</v>
       </c>
       <c r="L51" t="n">
-        <v>0.88</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
         <v>0.51</v>
       </c>
       <c r="N51" t="n">
-        <v>1.95</v>
+        <v>6.83</v>
       </c>
       <c r="O51" t="n">
         <v>-0.6</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.9</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>2380</v>
+        <v>2369.9</v>
       </c>
       <c r="I52" t="n">
         <v>2373.062012467705</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.23</v>
+        <v>-3.64</v>
       </c>
       <c r="L52" t="n">
         <v>5.85</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.31</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46085.55208333334</v>
+        <v>46086.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>2162.9</v>
+        <v>2393.4</v>
       </c>
       <c r="I53" t="n">
         <v>2308.207803335907</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K53" t="n">
-        <v>8.73</v>
+        <v>-0.99</v>
       </c>
       <c r="L53" t="n">
         <v>7.33</v>
@@ -3462,7 +4097,7 @@
         <v>2.34</v>
       </c>
       <c r="N53" t="n">
-        <v>3.04</v>
+        <v>8.93</v>
       </c>
       <c r="O53" t="n">
         <v>2.23</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>12.32</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>2326.9</v>
+        <v>2189.3</v>
       </c>
       <c r="I54" t="n">
         <v>2252.680345231312</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.78</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="L54" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="N54" t="n">
-        <v>5.03</v>
+        <v>5.39</v>
       </c>
       <c r="O54" t="n">
         <v>8.93</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>12.19</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46111.55208333334</v>
+        <v>46113.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>2068</v>
+        <v>2317</v>
       </c>
       <c r="I55" t="n">
         <v>2264.509006201211</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>5.54</v>
+        <v>-5.83</v>
       </c>
       <c r="L55" t="n">
-        <v>5.42</v>
+        <v>7.06</v>
       </c>
       <c r="M55" t="n">
-        <v>2.66</v>
+        <v>3.97</v>
       </c>
       <c r="N55" t="n">
-        <v>2.53</v>
+        <v>12.21</v>
       </c>
       <c r="O55" t="n">
         <v>-5.39</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>14.54</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46150.55208333334</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2656.8</v>
+        <v>2568.4</v>
       </c>
       <c r="I56" t="n">
         <v>2604.719435338146</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>14.67</v>
+        <v>10.85</v>
       </c>
       <c r="L56" t="n">
         <v>8.5</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.26</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>2469</v>
+        <v>2507.2</v>
       </c>
       <c r="I57" t="n">
         <v>2488.995357049126</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K57" t="n">
-        <v>3.87</v>
+        <v>2.38</v>
       </c>
       <c r="L57" t="n">
         <v>2.94</v>
@@ -3690,7 +4373,7 @@
         <v>1.32</v>
       </c>
       <c r="N57" t="n">
-        <v>2.68</v>
+        <v>3.69</v>
       </c>
       <c r="O57" t="n">
         <v>-3.49</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.68</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46211.55208333334</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>2453</v>
+        <v>2408</v>
       </c>
       <c r="I58" t="n">
         <v>2452.653237878516</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.16</v>
+        <v>-3.96</v>
       </c>
       <c r="L58" t="n">
-        <v>2.83</v>
+        <v>4.63</v>
       </c>
       <c r="M58" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="N58" t="n">
-        <v>2.41</v>
+        <v>3.27</v>
       </c>
       <c r="O58" t="n">
         <v>3.69</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.97</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>2326</v>
+        <v>2388.1</v>
       </c>
       <c r="I59" t="n">
         <v>2381.227910856064</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K59" t="n">
-        <v>3.41</v>
+        <v>0.83</v>
       </c>
       <c r="L59" t="n">
         <v>1.5</v>
       </c>
       <c r="M59" t="n">
-        <v>0.51</v>
+        <v>0.82</v>
       </c>
       <c r="N59" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="O59" t="n">
         <v>-3.27</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.37</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46265.38541666666</v>
+        <v>46265.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>2505.1</v>
+        <v>2497.8</v>
       </c>
       <c r="I60" t="n">
         <v>2504.037073570678</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>4.9</v>
+        <v>4.59</v>
       </c>
       <c r="L60" t="n">
         <v>2.48</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.86</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46308.38541666666</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>2095</v>
+        <v>2120.9</v>
       </c>
       <c r="I61" t="n">
         <v>2106.443659016717</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>42.83333333333334</v>
+        <v>43</v>
       </c>
       <c r="K61" t="n">
-        <v>16.13</v>
+        <v>15.09</v>
       </c>
       <c r="L61" t="n">
         <v>1.95</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>6.87</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>2051.6</v>
+        <v>1998.7</v>
       </c>
       <c r="I62" t="n">
         <v>2001.268719487647</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.27</v>
+        <v>-5.76</v>
       </c>
       <c r="L62" t="n">
-        <v>3.34</v>
+        <v>5.89</v>
       </c>
       <c r="M62" t="n">
         <v>0.33</v>
       </c>
       <c r="N62" t="n">
-        <v>1.84</v>
+        <v>2.72</v>
       </c>
       <c r="O62" t="n">
         <v>4.6</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,12 @@
       <c r="Q63" t="n">
         <v>10</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6137,7 +6898,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.3</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="6">
@@ -6147,7 +6908,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -6157,7 +6918,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145.8</v>
       </c>
     </row>
     <row r="8">
@@ -6167,7 +6928,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6177,7 +6938,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -6187,7 +6948,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -6227,7 +6988,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.32</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="15">
@@ -6237,7 +6998,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.85</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="16">
@@ -6247,7 +7008,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.57</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="17">
@@ -6257,7 +7018,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>218.64</v>
+        <v>203.67</v>
       </c>
     </row>
     <row r="18">
@@ -6267,7 +7028,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.4</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="19">
@@ -6277,7 +7038,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.99</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="20">
@@ -6287,7 +7048,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.85</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="21">
@@ -6297,7 +7058,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20.88</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="22">
@@ -6307,7 +7068,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -6317,7 +7078,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -6327,7 +7088,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="25">
@@ -6337,7 +7098,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.029999999999999</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="26">
@@ -6347,7 +7108,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.22</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="27">
@@ -6357,7 +7118,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15.67</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="28">
@@ -6367,7 +7128,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
